--- a/sources/jack2_step5.xlsx
+++ b/sources/jack2_step5.xlsx
@@ -920,6 +920,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
@@ -977,6 +982,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
@@ -1029,6 +1039,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
@@ -1079,6 +1094,11 @@
       <c r="O13" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>052a3efc-5cdf-4aa6-9af6-a58c6ed3b504</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -5879,6 +5899,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
+        </is>
+      </c>
       <c r="Q102" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
@@ -5911,6 +5936,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
+        </is>
+      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
@@ -5943,6 +5973,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+        </is>
+      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
@@ -5973,6 +6008,11 @@
       <c r="K105" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">

--- a/sources/jack2_step5.xlsx
+++ b/sources/jack2_step5.xlsx
@@ -3059,7 +3059,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4361,7 +4361,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4614,7 +4614,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5197,9 +5197,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
-        <f>~3+4</f>
-        <v/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -5254,6 +5255,11 @@
       <c r="Q87" t="inlineStr">
         <is>
           <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5301,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5343,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5347,6 +5353,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
@@ -5399,7 +5410,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5459,6 +5470,11 @@
       <c r="A92" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
